--- a/artfynd/A 61302-2022 artfynd.xlsx
+++ b/artfynd/A 61302-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61302-2022 artfynd.xlsx
+++ b/artfynd/A 61302-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106822290</v>
+        <v>131368967</v>
       </c>
       <c r="B2" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bornjöns Naturreservat, Srm</t>
+          <t>Fiskgjuseberget, Fiskgjuseberget, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655573.2664605866</v>
+        <v>656062</v>
       </c>
       <c r="R2" t="n">
-        <v>6570440.883457819</v>
+        <v>6569852</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Bornsjön</t>
-        </is>
-      </c>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106822238</v>
+        <v>106822290</v>
       </c>
       <c r="B3" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4363</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655653.2479508973</v>
+        <v>655574</v>
       </c>
       <c r="R3" t="n">
-        <v>6570442.110471436</v>
+        <v>6570441</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -861,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,48 +883,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131368597</v>
+        <v>106822238</v>
       </c>
       <c r="B4" t="n">
-        <v>91859</v>
+        <v>93193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fiskgjuseberget, Fiskgjuseberget, Srm</t>
+          <t>Bornjöns Naturreservat, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655990</v>
+        <v>655653</v>
       </c>
       <c r="R4" t="n">
-        <v>6569863</v>
+        <v>6570442</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,15 +968,126 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Bornsjön</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131368597</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fiskgjuseberget, Fiskgjuseberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>655990</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6569863</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61302-2022 artfynd.xlsx
+++ b/artfynd/A 61302-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131368967</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
           <t>Bornsjön</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106822290</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
           <t>Bornsjön</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106822238</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,8 +1108,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131368597</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>